--- a/Atividade3/tabela_curso_superior.xlsx
+++ b/Atividade3/tabela_curso_superior.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Regi?o</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
